--- a/Project Outputs for UZ_D_Resolver/Rev02/BOM/BOM_JLC-UZ_D_Resolver(Default)_w_JLC_part_no.xlsx
+++ b/Project Outputs for UZ_D_Resolver/Rev02/BOM/BOM_JLC-UZ_D_Resolver(Default)_w_JLC_part_no.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_d_resolver\Project Outputs for UZ_D_Resolver\Rev02\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ga92wum\git\UltraZohm\PCB\uz_d_resolver\Project Outputs for UZ_D_Resolver\Rev02\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16588F4D-E1E9-434A-A637-65F0BF372EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C9E055-9931-4634-B818-A7B82453045D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{7B1CB551-F52E-49A9-BFCD-BA492A3F477C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="185">
   <si>
     <t>Quantity</t>
   </si>
@@ -580,6 +580,9 @@
   </si>
   <si>
     <t>C19666</t>
+  </si>
+  <si>
+    <t>C434421</t>
   </si>
 </sst>
 </file>
@@ -956,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1849F93E-621C-41AA-8211-EF0089BC7336}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
@@ -971,7 +974,7 @@
     <col min="10" max="11" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>12</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>12</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>12</v>
       </c>
@@ -1130,7 +1133,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>9</v>
       </c>
@@ -1159,7 +1162,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>18</v>
       </c>
@@ -1190,7 +1193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>24</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1246,11 +1249,14 @@
       <c r="J9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -1279,7 +1285,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>6</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>7</v>
       </c>
@@ -1391,7 +1397,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>6</v>
       </c>
